--- a/_Drive/Publicacoes/robson.xlsx
+++ b/_Drive/Publicacoes/robson.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="robson.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,29 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1" count="1">
+  <si>
+    <t>DOI</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +80,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,301 +98,307 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="32.71231971153846" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcata.2011.09.030</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2006.10.023</t>
+          <t>10.1016/j.apcata.2011.09.030</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1016/j.electacta.2013.04.079</t>
+          <t>10.1016/j.jelechem.2006.10.023</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2014.02.009</t>
+          <t>10.1016/j.electacta.2013.04.079</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2013.04.008</t>
+          <t>10.1016/j.jelechem.2014.02.009</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1016/j.electacta.2012.09.113</t>
+          <t>10.1016/j.apcata.2013.04.008</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.electacta.2013.11.118</t>
+          <t>10.1016/j.electacta.2012.09.113</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.21577/0100-4042.20170163</t>
+          <t>10.1016/j.electacta.2013.11.118</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.5935/0103-5053.20140160</t>
+          <t>10.21577/0100-4042.20170163</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.matchemphys.2020.123651</t>
+          <t>10.5935/0103-5053.20140160</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.18011/bioeng2018v12n1p52-67</t>
+          <t>10.1016/j.matchemphys.2020.123651</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1016/j.colsurfa.2019.124034</t>
+          <t>10.18011/bioeng2018v12n1p52-67</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1016/j.ceramint.2020.02.249</t>
+          <t>10.1016/j.colsurfa.2019.124034</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1021/ie201317u</t>
+          <t>10.1016/j.ceramint.2020.02.249</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.4236/aces.2016.64037</t>
+          <t>10.1021/ie201317u</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2014.03.007</t>
+          <t>10.4236/aces.2016.64037</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1007/s11270-021-05039-w</t>
+          <t>10.1016/j.jelechem.2014.03.007</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1016/j.chemosphere.2016.07.070</t>
+          <t>10.1007/s11270-021-05039-w</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1016/j.chemosphere.2019.125807</t>
+          <t>10.1016/j.chemosphere.2016.07.070</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1007/s12678-020-00591-1</t>
+          <t>10.1016/j.chemosphere.2019.125807</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1016/j.carbon.2013.04.100</t>
+          <t>10.1007/s12678-020-00591-1</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2014.03.027</t>
+          <t>10.1016/j.carbon.2013.04.100</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1149/2.015409jes</t>
+          <t>10.1016/j.jelechem.2014.03.027</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2020.114746</t>
+          <t>10.1149/2.015409jes</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1016/j.diamond.2015.12.013</t>
+          <t>10.1016/j.jelechem.2020.114746</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1007/s11051-020-04893-9</t>
+          <t>10.1016/j.diamond.2015.12.013</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2012.12.003</t>
+          <t>10.1007/s11051-020-04893-9</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.2174/1573411013666180705142302</t>
+          <t>10.1016/j.jelechem.2012.12.003</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1149/2.0091414jes</t>
+          <t>10.2174/1573411013666180705142302</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2016.03.013</t>
+          <t>10.1149/2.0091414jes</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1016/j.apcatb.2013.05.024</t>
+          <t>10.1016/j.apcata.2016.03.013</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1016/j.ijleo.2020.165238</t>
+          <t>10.1016/j.apcatb.2013.05.024</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.1016/j.jelechem.2016.11.038</t>
+          <t>10.1016/j.ijleo.2020.165238</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1007/s12678-011-0063-0</t>
+          <t>10.1016/j.jelechem.2016.11.038</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1016/j.diamond.2012.11.008</t>
+          <t>10.1007/s12678-011-0063-0</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.1021/ie2026025</t>
+          <t>10.1016/j.diamond.2012.11.008</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.1016/j.jece.2017.08.041</t>
+          <t>10.1021/ie2026025</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1016/j.mseb.2021.115183</t>
+          <t>10.1016/j.jece.2017.08.041</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1016/j.electacta.2014.07.003</t>
+          <t>10.1016/j.mseb.2021.115183</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1016/j.electacta.2019.135013</t>
+          <t>10.1016/j.electacta.2014.07.003</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1007/s12678-010-0029-7</t>
+          <t>10.1016/j.electacta.2019.135013</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
+        <is>
+          <t>10.1007/s12678-010-0029-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>10.1016/j.ceramint.2020.06.166</t>
         </is>
